--- a/in_piura_plantillas/salida/Plantilla_Excel_Bloque_9_IN_Piura.xlsx
+++ b/in_piura_plantillas/salida/Plantilla_Excel_Bloque_9_IN_Piura.xlsx
@@ -120,7 +120,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="6">
     <border>
       <left/>
       <right/>
@@ -142,11 +142,55 @@
         <color rgb="009C9C9C"/>
       </bottom>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="009C9C9C"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="009C9C9C"/>
+      </right>
+      <top style="thin">
+        <color rgb="009C9C9C"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="009C9C9C"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="009C9C9C"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="009C9C9C"/>
+      </right>
+      <top style="thin">
+        <color rgb="009C9C9C"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="009C9C9C"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="36">
+  <cellXfs count="38">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -251,6 +295,8 @@
     <xf numFmtId="0" fontId="5" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -616,7 +662,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F54"/>
+  <dimension ref="A1:H56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -669,6 +715,7 @@
         </is>
       </c>
     </row>
+    <row r="7"/>
     <row r="8" ht="18" customHeight="1">
       <c r="A8" s="5" t="inlineStr">
         <is>
@@ -862,6 +909,7 @@
       <c r="E16" s="8" t="n"/>
       <c r="F16" s="8" t="n"/>
     </row>
+    <row r="17"/>
     <row r="18" ht="18" customHeight="1">
       <c r="A18" s="5" t="inlineStr">
         <is>
@@ -1027,6 +1075,7 @@
       <c r="E25" s="8" t="n"/>
       <c r="F25" s="8" t="n"/>
     </row>
+    <row r="26"/>
     <row r="27" ht="18" customHeight="1">
       <c r="A27" s="5" t="inlineStr">
         <is>
@@ -1064,7 +1113,7 @@
       </c>
       <c r="B29" s="7" t="inlineStr">
         <is>
-          <t>Sobre umbral</t>
+          <t>Sobre umbral · distribución areal: 11.54 % del bloque BAJO el umbral (12.678 ha de 109.860 ha)</t>
         </is>
       </c>
       <c r="C29" s="6" t="inlineStr">
@@ -1083,96 +1132,95 @@
     <row r="30">
       <c r="A30" s="6" t="inlineStr">
         <is>
-          <t>Superficie clasificada NDVI 2025 (ha)</t>
+          <t>MSAVI 2024 — superficie BAJO el umbral 0.4976 (ha)</t>
         </is>
       </c>
       <c r="B30" s="7" t="n">
-        <v>109.882</v>
+        <v>12.678</v>
       </c>
       <c r="C30" s="6" t="inlineStr">
         <is>
-          <t>Desviación frente al catálogo (%)</t>
+          <t>MSAVI 2024 — % del bloque BAJO el umbral</t>
         </is>
       </c>
       <c r="D30" s="7" t="n">
-        <v>0.02</v>
+        <v>11.54</v>
       </c>
       <c r="E30" s="8" t="n"/>
       <c r="F30" s="8" t="n"/>
     </row>
+    <row r="31">
+      <c r="A31" s="6" t="inlineStr">
+        <is>
+          <t>MSAVI 2024 — clase areal dominante</t>
+        </is>
+      </c>
+      <c r="B31" s="7" t="inlineStr">
+        <is>
+          <t>Vigor moderado</t>
+        </is>
+      </c>
+      <c r="C31" s="6" t="inlineStr">
+        <is>
+          <t>MSAVI 2024 — fuente de la distribución areal</t>
+        </is>
+      </c>
+      <c r="D31" s="7" t="inlineStr">
+        <is>
+          <t>Conteo de celdas sobre la cartografía MSAVI 2024 del bloque (9.png)</t>
+        </is>
+      </c>
+      <c r="E31" s="8" t="n"/>
+      <c r="F31" s="8" t="n"/>
+    </row>
     <row r="32" ht="18" customHeight="1">
-      <c r="A32" s="5" t="inlineStr">
+      <c r="A32" s="6" t="inlineStr">
+        <is>
+          <t>Superficie clasificada NDVI 2025 (ha)</t>
+        </is>
+      </c>
+      <c r="B32" s="7" t="n">
+        <v>109.882</v>
+      </c>
+      <c r="C32" s="6" t="inlineStr">
+        <is>
+          <t>Desviación frente al catálogo (%)</t>
+        </is>
+      </c>
+      <c r="D32" s="7" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="E32" s="8" t="n"/>
+      <c r="F32" s="8" t="n"/>
+    </row>
+    <row r="33"/>
+    <row r="34">
+      <c r="A34" s="5" t="inlineStr">
         <is>
           <t>4. ECOSISTEMA Y ESTADO DE CONSERVACIÓN</t>
         </is>
       </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="6" t="inlineStr">
-        <is>
-          <t>Tipo de ecosistema (UP)</t>
-        </is>
-      </c>
-      <c r="B33" s="7" t="inlineStr">
-        <is>
-          <t>Matorral Andino subhúmedo</t>
-        </is>
-      </c>
-      <c r="C33" s="6" t="inlineStr">
-        <is>
-          <t>Superficie de ecosistema (ha)</t>
-        </is>
-      </c>
-      <c r="D33" s="7" t="inlineStr">
-        <is>
-          <t>109.861 ha</t>
-        </is>
-      </c>
-      <c r="E33" s="8" t="n"/>
-      <c r="F33" s="8" t="n"/>
-    </row>
-    <row r="34">
-      <c r="A34" s="6" t="inlineStr">
-        <is>
-          <t>Estado de conservación</t>
-        </is>
-      </c>
-      <c r="B34" s="7" t="inlineStr">
-        <is>
-          <t>Medianamente alterado</t>
-        </is>
-      </c>
-      <c r="C34" s="6" t="inlineStr">
-        <is>
-          <t>Uso actual dominante del suelo</t>
-        </is>
-      </c>
-      <c r="D34" s="7" t="inlineStr">
-        <is>
-          <t>Agricultura secano</t>
-        </is>
-      </c>
-      <c r="E34" s="8" t="n"/>
-      <c r="F34" s="8" t="n"/>
     </row>
     <row r="35">
       <c r="A35" s="6" t="inlineStr">
         <is>
-          <t>Tipo de cobertura dominante</t>
+          <t>Tipo de ecosistema (UP)</t>
         </is>
       </c>
       <c r="B35" s="7" t="inlineStr">
         <is>
-          <t>Matorral ralo</t>
+          <t>Matorral Andino subhúmedo</t>
         </is>
       </c>
       <c r="C35" s="6" t="inlineStr">
         <is>
-          <t>Cobertura vegetal total — campo (%)</t>
-        </is>
-      </c>
-      <c r="D35" s="7" t="n">
-        <v>40</v>
+          <t>Superficie de ecosistema (ha)</t>
+        </is>
+      </c>
+      <c r="D35" s="7" t="inlineStr">
+        <is>
+          <t>109.861 ha</t>
+        </is>
       </c>
       <c r="E35" s="8" t="n"/>
       <c r="F35" s="8" t="n"/>
@@ -1180,20 +1228,22 @@
     <row r="36">
       <c r="A36" s="6" t="inlineStr">
         <is>
-          <t>Suelo desnudo — campo (%)</t>
-        </is>
-      </c>
-      <c r="B36" s="7" t="n">
-        <v>25</v>
+          <t>Estado de conservación</t>
+        </is>
+      </c>
+      <c r="B36" s="7" t="inlineStr">
+        <is>
+          <t>Medianamente alterado</t>
+        </is>
       </c>
       <c r="C36" s="6" t="inlineStr">
         <is>
-          <t>Regeneración natural</t>
+          <t>Uso actual dominante del suelo</t>
         </is>
       </c>
       <c r="D36" s="7" t="inlineStr">
         <is>
-          <t>Escasa (&lt;10 pl./100m²)</t>
+          <t>Agricultura secano</t>
         </is>
       </c>
       <c r="E36" s="8" t="n"/>
@@ -1202,21 +1252,21 @@
     <row r="37">
       <c r="A37" s="6" t="inlineStr">
         <is>
-          <t>Nivel general de erosión</t>
+          <t>Tipo de cobertura dominante</t>
         </is>
       </c>
       <c r="B37" s="7" t="inlineStr">
         <is>
-          <t>Moderada (surcos)</t>
+          <t>Matorral ralo</t>
         </is>
       </c>
       <c r="C37" s="6" t="inlineStr">
         <is>
-          <t>N.° de cárcavas registradas</t>
+          <t>Cobertura vegetal total — campo (%)</t>
         </is>
       </c>
       <c r="D37" s="7" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="E37" s="8" t="n"/>
       <c r="F37" s="8" t="n"/>
@@ -1224,99 +1274,96 @@
     <row r="38">
       <c r="A38" s="6" t="inlineStr">
         <is>
-          <t>Elenco florístico (n.° de taxones)</t>
+          <t>Suelo desnudo — campo (%)</t>
         </is>
       </c>
       <c r="B38" s="7" t="n">
-        <v>11</v>
+        <v>25</v>
       </c>
       <c r="C38" s="6" t="inlineStr">
         <is>
-          <t>Estado sanitario</t>
+          <t>Regeneración natural</t>
         </is>
       </c>
       <c r="D38" s="7" t="inlineStr">
         <is>
-          <t>Sano</t>
+          <t>Escasa (&lt;10 pl./100m²)</t>
         </is>
       </c>
       <c r="E38" s="8" t="n"/>
       <c r="F38" s="8" t="n"/>
     </row>
+    <row r="39">
+      <c r="A39" s="6" t="inlineStr">
+        <is>
+          <t>Nivel general de erosión</t>
+        </is>
+      </c>
+      <c r="B39" s="7" t="inlineStr">
+        <is>
+          <t>Moderada (surcos)</t>
+        </is>
+      </c>
+      <c r="C39" s="6" t="inlineStr">
+        <is>
+          <t>N.° de cárcavas registradas</t>
+        </is>
+      </c>
+      <c r="D39" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E39" s="8" t="n"/>
+      <c r="F39" s="8" t="n"/>
+    </row>
     <row r="40" ht="18" customHeight="1">
-      <c r="A40" s="5" t="inlineStr">
+      <c r="A40" s="6" t="inlineStr">
+        <is>
+          <t>Elenco florístico (n.° de taxones)</t>
+        </is>
+      </c>
+      <c r="B40" s="7" t="n">
+        <v>11</v>
+      </c>
+      <c r="C40" s="6" t="inlineStr">
+        <is>
+          <t>Estado sanitario</t>
+        </is>
+      </c>
+      <c r="D40" s="7" t="inlineStr">
+        <is>
+          <t>Sano</t>
+        </is>
+      </c>
+      <c r="E40" s="8" t="n"/>
+      <c r="F40" s="8" t="n"/>
+    </row>
+    <row r="41"/>
+    <row r="42">
+      <c r="A42" s="5" t="inlineStr">
         <is>
           <t>5. RESPONSABLE Y MODALIDAD DE LA EVALUACIÓN</t>
         </is>
       </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="6" t="inlineStr">
-        <is>
-          <t>Responsable de la evaluación</t>
-        </is>
-      </c>
-      <c r="B41" s="7" t="inlineStr">
-        <is>
-          <t>Ing. Pedro Talledo Hernández</t>
-        </is>
-      </c>
-      <c r="C41" s="6" t="inlineStr">
-        <is>
-          <t>Fecha de evaluación</t>
-        </is>
-      </c>
-      <c r="D41" s="7" t="inlineStr">
-        <is>
-          <t>2026-08-11</t>
-        </is>
-      </c>
-      <c r="E41" s="8" t="n"/>
-      <c r="F41" s="8" t="n"/>
-    </row>
-    <row r="42">
-      <c r="A42" s="6" t="inlineStr">
-        <is>
-          <t>Hora de registro</t>
-        </is>
-      </c>
-      <c r="B42" s="7" t="inlineStr">
-        <is>
-          <t>Por registrar</t>
-        </is>
-      </c>
-      <c r="C42" s="6" t="inlineStr">
-        <is>
-          <t>Correlativo de ficha</t>
-        </is>
-      </c>
-      <c r="D42" s="7" t="inlineStr">
-        <is>
-          <t>F-DT-09-01</t>
-        </is>
-      </c>
-      <c r="E42" s="8" t="n"/>
-      <c r="F42" s="8" t="n"/>
     </row>
     <row r="43">
       <c r="A43" s="6" t="inlineStr">
         <is>
-          <t>Entidad</t>
+          <t>Responsable de la evaluación</t>
         </is>
       </c>
       <c r="B43" s="7" t="inlineStr">
         <is>
-          <t>ANIN - DIME - SESDI</t>
+          <t>Ing. Pedro Talledo Hernández</t>
         </is>
       </c>
       <c r="C43" s="6" t="inlineStr">
         <is>
-          <t>Fase del estudio</t>
+          <t>Fecha de evaluación</t>
         </is>
       </c>
       <c r="D43" s="7" t="inlineStr">
         <is>
-          <t>Preinversión (Perfil) · Invierte.pe</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="E43" s="8" t="n"/>
@@ -1325,22 +1372,22 @@
     <row r="44">
       <c r="A44" s="6" t="inlineStr">
         <is>
-          <t>Instrumento aplicado</t>
+          <t>Hora de registro</t>
         </is>
       </c>
       <c r="B44" s="7" t="inlineStr">
         <is>
-          <t>Fichas F-DT-01 a F-DT-05 (Plantilla V5)</t>
+          <t>Por registrar</t>
         </is>
       </c>
       <c r="C44" s="6" t="inlineStr">
         <is>
-          <t>Parcela de muestreo</t>
+          <t>Correlativo de ficha</t>
         </is>
       </c>
       <c r="D44" s="7" t="inlineStr">
         <is>
-          <t>P-01</t>
+          <t>F-DT-09-01</t>
         </is>
       </c>
       <c r="E44" s="8" t="n"/>
@@ -1349,101 +1396,102 @@
     <row r="45">
       <c r="A45" s="6" t="inlineStr">
         <is>
-          <t>Estaciones fotográficas georreferenciadas</t>
+          <t>Entidad</t>
         </is>
       </c>
       <c r="B45" s="7" t="inlineStr">
         <is>
-          <t>Sin registro en la ficha DT</t>
+          <t>ANIN - DIME - SESDI</t>
         </is>
       </c>
       <c r="C45" s="6" t="inlineStr">
         <is>
-          <t>Modalidad de acceso</t>
+          <t>Fase del estudio</t>
         </is>
       </c>
       <c r="D45" s="7" t="inlineStr">
         <is>
-          <t>Vehicular + caminata 30-90 min</t>
+          <t>Preinversión (Perfil) · Invierte.pe</t>
         </is>
       </c>
       <c r="E45" s="8" t="n"/>
       <c r="F45" s="8" t="n"/>
     </row>
+    <row r="46">
+      <c r="A46" s="6" t="inlineStr">
+        <is>
+          <t>Instrumento aplicado</t>
+        </is>
+      </c>
+      <c r="B46" s="7" t="inlineStr">
+        <is>
+          <t>Fichas F-DT-01 a F-DT-05 (Plantilla V5)</t>
+        </is>
+      </c>
+      <c r="C46" s="6" t="inlineStr">
+        <is>
+          <t>Parcela de muestreo</t>
+        </is>
+      </c>
+      <c r="D46" s="7" t="inlineStr">
+        <is>
+          <t>P-01</t>
+        </is>
+      </c>
+      <c r="E46" s="8" t="n"/>
+      <c r="F46" s="8" t="n"/>
+    </row>
     <row r="47" ht="18" customHeight="1">
-      <c r="A47" s="5" t="inlineStr">
+      <c r="A47" s="6" t="inlineStr">
+        <is>
+          <t>Estaciones fotográficas georreferenciadas</t>
+        </is>
+      </c>
+      <c r="B47" s="7" t="inlineStr">
+        <is>
+          <t>Sin registro en la ficha DT</t>
+        </is>
+      </c>
+      <c r="C47" s="6" t="inlineStr">
+        <is>
+          <t>Modalidad de acceso</t>
+        </is>
+      </c>
+      <c r="D47" s="7" t="inlineStr">
+        <is>
+          <t>Vehicular + caminata 30-90 min</t>
+        </is>
+      </c>
+      <c r="E47" s="8" t="n"/>
+      <c r="F47" s="8" t="n"/>
+    </row>
+    <row r="48"/>
+    <row r="49">
+      <c r="A49" s="5" t="inlineStr">
         <is>
           <t>6. SÍNTESIS PARA LA GESTIÓN DEL RIESGO EN CONTEXTO DE CAMBIO CLIMÁTICO</t>
         </is>
       </c>
-    </row>
-    <row r="48">
-      <c r="A48" s="6" t="inlineStr">
-        <is>
-          <t>Causa subyacente principal</t>
-        </is>
-      </c>
-      <c r="B48" s="7" t="inlineStr">
-        <is>
-          <t>Presión demográfica y necesidad de tierras para cultivo y pastoreo de subsistencia</t>
-        </is>
-      </c>
-      <c r="C48" s="6" t="inlineStr">
-        <is>
-          <t>Velocidad de degradación</t>
-        </is>
-      </c>
-      <c r="D48" s="7" t="inlineStr">
-        <is>
-          <t>Moderada</t>
-        </is>
-      </c>
-      <c r="E48" s="8" t="n"/>
-      <c r="F48" s="8" t="n"/>
-    </row>
-    <row r="49">
-      <c r="A49" s="6" t="inlineStr">
-        <is>
-          <t>Reversibilidad técnica</t>
-        </is>
-      </c>
-      <c r="B49" s="7" t="inlineStr">
-        <is>
-          <t>Parcialmente reversible</t>
-        </is>
-      </c>
-      <c r="C49" s="6" t="inlineStr">
-        <is>
-          <t>Urgencia de intervención</t>
-        </is>
-      </c>
-      <c r="D49" s="7" t="inlineStr">
-        <is>
-          <t>Alta</t>
-        </is>
-      </c>
-      <c r="E49" s="8" t="n"/>
-      <c r="F49" s="8" t="n"/>
     </row>
     <row r="50">
       <c r="A50" s="6" t="inlineStr">
         <is>
-          <t>Urgencia de control de erosión</t>
+          <t>Causa subyacente principal</t>
         </is>
       </c>
       <c r="B50" s="7" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Presión demográfica y necesidad de tierras para cultivo y pastoreo de subsistencia</t>
         </is>
       </c>
       <c r="C50" s="6" t="inlineStr">
         <is>
-          <t>Zona de recarga hídrica</t>
+          <t>Velocidad de degradación</t>
         </is>
       </c>
       <c r="D50" s="7" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>Moderada</t>
         </is>
       </c>
       <c r="E50" s="8" t="n"/>
@@ -1452,22 +1500,22 @@
     <row r="51">
       <c r="A51" s="6" t="inlineStr">
         <is>
-          <t>Peligro integrado preliminar (MCA-AHP)</t>
+          <t>Reversibilidad técnica</t>
         </is>
       </c>
       <c r="B51" s="7" t="inlineStr">
         <is>
-          <t>No disponible en los insumos; debe tomarse del modelamiento de mesolocalización</t>
+          <t>Parcialmente reversible</t>
         </is>
       </c>
       <c r="C51" s="6" t="inlineStr">
         <is>
-          <t>Prioridad de intervención</t>
+          <t>Urgencia de intervención</t>
         </is>
       </c>
       <c r="D51" s="7" t="inlineStr">
         <is>
-          <t>Por definir en mesolocalización</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="E51" s="8" t="n"/>
@@ -1476,49 +1524,103 @@
     <row r="52">
       <c r="A52" s="6" t="inlineStr">
         <is>
-          <t>Estado de verificación de campo</t>
+          <t>Urgencia de control de erosión</t>
         </is>
       </c>
       <c r="B52" s="7" t="inlineStr">
         <is>
-          <t>VERIFICADO</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="C52" s="6" t="inlineStr">
         <is>
-          <t>Marco del indicador de brecha</t>
+          <t>Zona de recarga hídrica</t>
         </is>
       </c>
       <c r="D52" s="7" t="inlineStr">
         <is>
-          <t>R.M. N.° 00213-2024-MINAM</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="E52" s="8" t="n"/>
       <c r="F52" s="8" t="n"/>
     </row>
+    <row r="53">
+      <c r="A53" s="6" t="inlineStr">
+        <is>
+          <t>Peligro integrado preliminar (MCA-AHP)</t>
+        </is>
+      </c>
+      <c r="B53" s="7" t="inlineStr">
+        <is>
+          <t>No disponible en los insumos; debe tomarse del modelamiento de mesolocalización</t>
+        </is>
+      </c>
+      <c r="C53" s="6" t="inlineStr">
+        <is>
+          <t>Prioridad de intervención</t>
+        </is>
+      </c>
+      <c r="D53" s="7" t="inlineStr">
+        <is>
+          <t>Por definir en mesolocalización</t>
+        </is>
+      </c>
+      <c r="E53" s="8" t="n"/>
+      <c r="F53" s="8" t="n"/>
+    </row>
     <row r="54" ht="72" customHeight="1">
-      <c r="A54" s="9" t="inlineStr">
+      <c r="A54" s="6" t="inlineStr">
+        <is>
+          <t>Estado de verificación de campo</t>
+        </is>
+      </c>
+      <c r="B54" s="7" t="inlineStr">
+        <is>
+          <t>VERIFICADO</t>
+        </is>
+      </c>
+      <c r="C54" s="6" t="inlineStr">
+        <is>
+          <t>Marco del indicador de brecha</t>
+        </is>
+      </c>
+      <c r="D54" s="7" t="inlineStr">
+        <is>
+          <t>R.M. N.° 00213-2024-MINAM</t>
+        </is>
+      </c>
+      <c r="E54" s="8" t="n"/>
+      <c r="F54" s="8" t="n"/>
+    </row>
+    <row r="55"/>
+    <row r="56">
+      <c r="A56" s="9" t="inlineStr">
         <is>
           <t>DECLARACIÓN DE INTEGRIDAD DE DATOS. Ningún valor ausente ha sido estimado o inferido sin declararlo. Los campos que no pudieron sustentarse en observación de campo, estadística zonal o catálogo oficial se consignan como «Por determinar» o «Por verificar». La altitud y la pendiente proceden de estadística zonal sobre el modelo digital de elevación; el MSAVI 2024 y el NDVI mediana 2025 proceden de compuestos Sentinel-2. Las discrepancias detectadas entre campo, gabinete y catálogo se listan en la hoja «Control de consistencia».</t>
         </is>
       </c>
+      <c r="B56" s="36" t="n"/>
+      <c r="C56" s="36" t="n"/>
+      <c r="D56" s="36" t="n"/>
+      <c r="E56" s="36" t="n"/>
+      <c r="F56" s="37" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="13">
+    <mergeCell ref="A27:F27"/>
+    <mergeCell ref="A34:F34"/>
+    <mergeCell ref="A18:F18"/>
+    <mergeCell ref="A56:F56"/>
+    <mergeCell ref="A3:F3"/>
     <mergeCell ref="A2:F2"/>
-    <mergeCell ref="A54:F54"/>
-    <mergeCell ref="A47:F47"/>
+    <mergeCell ref="A49:F49"/>
+    <mergeCell ref="A42:F42"/>
     <mergeCell ref="A1:F1"/>
     <mergeCell ref="A5:F5"/>
-    <mergeCell ref="A32:F32"/>
-    <mergeCell ref="A27:F27"/>
     <mergeCell ref="A8:F8"/>
     <mergeCell ref="A6:F6"/>
-    <mergeCell ref="A40:F40"/>
-    <mergeCell ref="A18:F18"/>
     <mergeCell ref="A4:F4"/>
-    <mergeCell ref="A3:F3"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1530,7 +1632,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E27"/>
+  <dimension ref="A1:H28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -1582,6 +1684,7 @@
         </is>
       </c>
     </row>
+    <row r="7"/>
     <row r="8" ht="18" customHeight="1">
       <c r="A8" s="5" t="inlineStr">
         <is>
@@ -1622,15 +1725,11 @@
           <t>&gt; 0.6139</t>
         </is>
       </c>
-      <c r="B10" s="11" t="inlineStr">
-        <is>
-          <t>Por determinar</t>
-        </is>
-      </c>
-      <c r="C10" s="11" t="inlineStr">
-        <is>
-          <t>Por determinar</t>
-        </is>
+      <c r="B10" s="18" t="n">
+        <v>29.9368</v>
+      </c>
+      <c r="C10" s="19" t="n">
+        <v>27.25</v>
       </c>
       <c r="D10" s="11" t="inlineStr">
         <is>
@@ -1649,15 +1748,11 @@
           <t>0.4976 - 0.6139</t>
         </is>
       </c>
-      <c r="B11" s="13" t="inlineStr">
-        <is>
-          <t>Por determinar</t>
-        </is>
-      </c>
-      <c r="C11" s="13" t="inlineStr">
-        <is>
-          <t>Por determinar</t>
-        </is>
+      <c r="B11" s="28" t="n">
+        <v>67.2454</v>
+      </c>
+      <c r="C11" s="27" t="n">
+        <v>61.21</v>
       </c>
       <c r="D11" s="13" t="inlineStr">
         <is>
@@ -1676,15 +1771,11 @@
           <t>0.3813 - 0.4976</t>
         </is>
       </c>
-      <c r="B12" s="11" t="inlineStr">
-        <is>
-          <t>Por determinar</t>
-        </is>
-      </c>
-      <c r="C12" s="11" t="inlineStr">
-        <is>
-          <t>Por determinar</t>
-        </is>
+      <c r="B12" s="18" t="n">
+        <v>12.2933</v>
+      </c>
+      <c r="C12" s="19" t="n">
+        <v>11.19</v>
       </c>
       <c r="D12" s="11" t="inlineStr">
         <is>
@@ -1703,15 +1794,11 @@
           <t>0.2650 - 0.3813</t>
         </is>
       </c>
-      <c r="B13" s="15" t="inlineStr">
-        <is>
-          <t>Por determinar</t>
-        </is>
-      </c>
-      <c r="C13" s="15" t="inlineStr">
-        <is>
-          <t>Por determinar</t>
-        </is>
+      <c r="B13" s="20" t="n">
+        <v>0.3845</v>
+      </c>
+      <c r="C13" s="21" t="n">
+        <v>0.35</v>
       </c>
       <c r="D13" s="15" t="inlineStr">
         <is>
@@ -1730,15 +1817,11 @@
           <t>&lt;= 0.2650</t>
         </is>
       </c>
-      <c r="B14" s="11" t="inlineStr">
-        <is>
-          <t>Por determinar</t>
-        </is>
-      </c>
-      <c r="C14" s="11" t="inlineStr">
-        <is>
-          <t>Por determinar</t>
-        </is>
+      <c r="B14" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="C14" s="19" t="n">
+        <v>0</v>
       </c>
       <c r="D14" s="11" t="inlineStr">
         <is>
@@ -1752,188 +1835,224 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="16" t="inlineStr">
+      <c r="A15" s="7" t="inlineStr">
+        <is>
+          <t>TOTAL CLASIFICADO</t>
+        </is>
+      </c>
+      <c r="B15" s="18">
+        <f>SUM(B10:B14)</f>
+        <v/>
+      </c>
+      <c r="C15" s="19">
+        <f>SUM(C10:C14)</f>
+        <v/>
+      </c>
+      <c r="D15" s="11" t="inlineStr">
+        <is>
+          <t>Suma de las cinco clases MSAVI 2024</t>
+        </is>
+      </c>
+      <c r="E15" s="11" t="inlineStr">
+        <is>
+          <t>Iguala la superficie de catálogo (V5/V6)</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="16" t="inlineStr">
         <is>
           <t>MSAVI 2024 — MEDIA DEL BLOQUE</t>
         </is>
       </c>
-      <c r="B15" s="17" t="n">
+      <c r="B16" s="17" t="n">
         <v>0.574527</v>
       </c>
-      <c r="C15" s="17" t="inlineStr">
+      <c r="C16" s="17" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="D15" s="17" t="inlineStr">
+      <c r="D16" s="17" t="inlineStr">
         <is>
           <t>Vigor moderado · clase 0.4976 - 0.6139</t>
         </is>
       </c>
-      <c r="E15" s="17" t="inlineStr">
+      <c r="E16" s="17" t="inlineStr">
         <is>
           <t>Sobre umbral</t>
         </is>
       </c>
     </row>
-    <row r="17" ht="72" customHeight="1">
-      <c r="A17" s="9" t="inlineStr">
-        <is>
-          <t>NOTA METODOLÓGICA. La media del MSAVI 2024 del bloque (0.574527) procede del catálogo maestro de bloques V5/V6 y es dato oficial. La DISTRIBUCIÓN AREAL por clase de MSAVI no está disponible como estadística zonal en los insumos de este entregable: se consigna «Por determinar» y NO se estima, conforme a la declaración de integridad de datos del proyecto. La fila resaltada indica la clase en la que cae la media del bloque. Para el dimensionamiento de metas físicas debe ejecutarse estadística zonal directa sobre el ráster MSAVI 2024 recortado al polígono.</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="18" customHeight="1">
-      <c r="A19" s="5" t="inlineStr">
+    <row r="17" ht="72" customHeight="1"/>
+    <row r="18">
+      <c r="A18" s="9" t="inlineStr">
+        <is>
+          <t>NOTA METODOLÓGICA. La media del MSAVI 2024 del bloque procede del catálogo maestro de bloques V5/V6 y es dato oficial. La DISTRIBUCIÓN AREAL por clase se obtuvo por conteo de celdas sobre la cartografía temática MSAVI 2024 del bloque (carpeta Drive «MSAVI BLOQUES V6»), clasificada con la paleta RdYlGn de cinco clases y los mismos umbrales del proyecto. El reparto porcentual es el medido sobre el polígono del bloque; las hectáreas se obtienen aplicando ese reparto a la superficie de catálogo (V5/V6) declarada en la hoja «Resumen», de modo que el total por clase cuadra con la superficie oficial. Umbral de brecha 0.4976 conforme a la R.M. N.° 00213-2024-MINAM. CONTRASTE INDEPENDIENTE: la tabla de intersección vectorial «BLOQUES_V6_INTERSECC_MSAVI» reproduce el mismo ordenamiento de bloques (correlación de Pearson 0.949 sobre el porcentaje bajo umbral en los 117 bloques); no se usa para el metrado porque su campo AREA_M2 conserva el área del polígono padre y no la de cada pieza de intersección. El refrendo por estadística zonal directa sobre el ráster MSAVI 2024 recortado al polígono queda pendiente.</t>
+        </is>
+      </c>
+      <c r="B18" s="36" t="n"/>
+      <c r="C18" s="36" t="n"/>
+      <c r="D18" s="36" t="n"/>
+      <c r="E18" s="37" t="n"/>
+    </row>
+    <row r="19" ht="18" customHeight="1"/>
+    <row r="20" ht="28" customHeight="1">
+      <c r="A20" s="5" t="inlineStr">
         <is>
           <t>B. NDVI MEDIANA 2025 — DISTRIBUCIÓN AREAL (ESTADÍSTICA ZONAL)</t>
         </is>
       </c>
     </row>
-    <row r="20" ht="28" customHeight="1">
-      <c r="A20" s="10" t="inlineStr">
+    <row r="21">
+      <c r="A21" s="10" t="inlineStr">
         <is>
           <t>Clase NDVI</t>
         </is>
       </c>
-      <c r="B20" s="10" t="inlineStr">
+      <c r="B21" s="10" t="inlineStr">
         <is>
           <t>Superficie (ha)</t>
         </is>
       </c>
-      <c r="C20" s="10" t="inlineStr">
+      <c r="C21" s="10" t="inlineStr">
         <is>
           <t>% del área clasificada</t>
         </is>
       </c>
-      <c r="D20" s="10" t="inlineStr">
+      <c r="D21" s="10" t="inlineStr">
         <is>
           <t>Interpretación</t>
         </is>
       </c>
-      <c r="E20" s="10" t="inlineStr">
+      <c r="E21" s="10" t="inlineStr">
         <is>
           <t>Observación</t>
         </is>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" s="7" t="inlineStr">
+    <row r="22">
+      <c r="A22" s="7" t="inlineStr">
         <is>
           <t>Vegetación alta</t>
         </is>
       </c>
-      <c r="B21" s="18" t="n">
+      <c r="B22" s="18" t="n">
         <v>99.1632</v>
       </c>
-      <c r="C21" s="19" t="n">
+      <c r="C22" s="19" t="n">
         <v>90.23999999999999</v>
       </c>
-      <c r="D21" s="11" t="inlineStr">
+      <c r="D22" s="11" t="inlineStr">
         <is>
           <t>Dosel continuo, matorral denso o mosaico agroforestal</t>
         </is>
       </c>
-      <c r="E21" s="11" t="inlineStr"/>
-    </row>
-    <row r="22">
-      <c r="A22" s="14" t="inlineStr">
+      <c r="E22" s="11" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="14" t="inlineStr">
         <is>
           <t>Vegetación mediana</t>
         </is>
       </c>
-      <c r="B22" s="20" t="n">
+      <c r="B23" s="20" t="n">
         <v>10.5789</v>
       </c>
-      <c r="C22" s="21" t="n">
+      <c r="C23" s="21" t="n">
         <v>9.630000000000001</v>
       </c>
-      <c r="D22" s="15" t="inlineStr">
+      <c r="D23" s="15" t="inlineStr">
         <is>
           <t>Pastizal cultivado, matorral ralo, parcelas agrícolas</t>
         </is>
       </c>
-      <c r="E22" s="15" t="inlineStr"/>
-    </row>
-    <row r="23">
-      <c r="A23" s="7" t="inlineStr">
+      <c r="E23" s="15" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="7" t="inlineStr">
         <is>
           <t>Vegetación ligera</t>
         </is>
       </c>
-      <c r="B23" s="18" t="n">
+      <c r="B24" s="18" t="n">
         <v>0.1404</v>
       </c>
-      <c r="C23" s="19" t="n">
+      <c r="C24" s="19" t="n">
         <v>0.13</v>
       </c>
-      <c r="D23" s="11" t="inlineStr">
+      <c r="D24" s="11" t="inlineStr">
         <is>
           <t>Cobertura discontinua, suelo parcialmente expuesto</t>
         </is>
       </c>
-      <c r="E23" s="11" t="inlineStr"/>
-    </row>
-    <row r="24">
-      <c r="A24" s="16" t="inlineStr">
+      <c r="E24" s="11" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="16" t="inlineStr">
         <is>
           <t>TOTAL CLASIFICADO</t>
         </is>
       </c>
-      <c r="B24" s="22">
+      <c r="B25" s="22">
         <f>SUM(B21:B23)</f>
         <v/>
       </c>
-      <c r="C24" s="23">
+      <c r="C25" s="23">
         <f>SUM(C21:C23)</f>
         <v/>
       </c>
-      <c r="D24" s="17" t="inlineStr"/>
-      <c r="E24" s="17" t="inlineStr"/>
-    </row>
-    <row r="25">
-      <c r="A25" s="24" t="inlineStr">
+      <c r="D25" s="17" t="inlineStr"/>
+      <c r="E25" s="17" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="24" t="inlineStr">
         <is>
           <t>Superficie de catálogo (V5/V6)</t>
         </is>
       </c>
-      <c r="B25" s="25" t="n">
+      <c r="B26" s="25" t="n">
         <v>109.86</v>
       </c>
-      <c r="C25" s="25" t="inlineStr">
+      <c r="C26" s="25" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="D25" s="25" t="inlineStr">
+      <c r="D26" s="25" t="inlineStr">
         <is>
           <t>Desviación planimétrica frente al catálogo</t>
         </is>
       </c>
-      <c r="E25" s="25" t="inlineStr">
+      <c r="E26" s="25" t="inlineStr">
         <is>
           <t>+0.02 %</t>
         </is>
       </c>
     </row>
-    <row r="27" ht="108" customHeight="1">
-      <c r="A27" s="9" t="inlineStr">
+    <row r="27" ht="108" customHeight="1"/>
+    <row r="28">
+      <c r="A28" s="9" t="inlineStr">
         <is>
           <t>LECTURA CRÍTICA. Los índices MSAVI y NDVI miden vigor y densidad de biomasa, no composición ni integridad ecosistémica. Un valor alto NO equivale a ausencia de degradación: en bloques con mosaico agrícola, pastizal cultivado o plantaciones, la respuesta espectral puede ser alta sobre una unidad productora sustituida en su composición. La diferencia entre ambos productos no debe leerse como mejora entre 2024 y 2025: son índices distintos (el NDVI satura ante biomasa densa, el MSAVI conserva sensibilidad al suelo de fondo) aplicados sobre compuestos temporales distintos. Contraste registrado en este bloque: la cobertura vegetal estimada en campo es 40 % frente a un 90.24 % del polígono clasificado como «Vegetación alta» por el NDVI 2025; la observación de campo corresponde a una parcela o recorrido puntual y no es estadísticamente representativa de las 109.860 ha del bloque.</t>
         </is>
       </c>
+      <c r="B28" s="36" t="n"/>
+      <c r="C28" s="36" t="n"/>
+      <c r="D28" s="36" t="n"/>
+      <c r="E28" s="37" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="10">
     <mergeCell ref="A4:E4"/>
+    <mergeCell ref="A20:E20"/>
     <mergeCell ref="A2:E2"/>
-    <mergeCell ref="A19:E19"/>
+    <mergeCell ref="A28:E28"/>
+    <mergeCell ref="A5:E5"/>
     <mergeCell ref="A1:E1"/>
-    <mergeCell ref="A5:E5"/>
     <mergeCell ref="A8:E8"/>
     <mergeCell ref="A6:E6"/>
-    <mergeCell ref="A17:E17"/>
-    <mergeCell ref="A27:E27"/>
+    <mergeCell ref="A18:E18"/>
     <mergeCell ref="A3:E3"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2119,6 +2238,12 @@
           <t>CONTROL GEOMÉTRICO. Las coordenadas de esta hoja proceden de la ficha DT del bloque (F-DT-01 a F-DT-05) y corresponden a rasgos erosivos, fuentes de agua, especies clave y al punto de muestreo declarado. La distancia al centroide se calcula sobre coordenadas UTM 17S y es referencial: no acredita inclusión ni exclusión respecto del polígono, que exige prueba de inclusión sobre la geometría del bloque. Las estaciones situadas a menos de ~30 m del límite deben considerarse SOBRE EL LÍMITE, dentro del margen de error de la georreferenciación (± 10-15 m). Bloque con predominio de pendientes muy fuertes (&gt;27° en el 93% del área), altamente susceptible a procesos erosivos si se pierde la cobertura vegetal.</t>
         </is>
       </c>
+      <c r="B15" s="36" t="n"/>
+      <c r="C15" s="36" t="n"/>
+      <c r="D15" s="36" t="n"/>
+      <c r="E15" s="36" t="n"/>
+      <c r="F15" s="36" t="n"/>
+      <c r="G15" s="37" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="8">
@@ -2494,6 +2619,13 @@
           <t>LECTURA INTRAMICROCUENCA. El bloque 9 ocupa el puesto 1 de 7 por superficie dentro de la microcuenca C1076-Q9586 (40.10 % de las 273.96 ha preliminares de la microcuenca). Su pendiente promedio (34.82 %, clase «25-50% (Mod. escarpado)») es la 7.ª más baja de 7 y se sitúa por encima del promedio de la microcuenca (29.26 %). Su MSAVI 2024 (0.5745) es el 5.º de 7 y queda por debajo del promedio local (0.5793). Amplitud altitudinal del bloque: 735 m (1529–2264 msnm). El cuadro conserva todos los bloques catalogados en la microcuenca, incluidos los descartados en el tamizaje, para referencia del conjunto. Los bloques sin ficha DT figuran con sus parámetros de gabinete.</t>
         </is>
       </c>
+      <c r="B19" s="36" t="n"/>
+      <c r="C19" s="36" t="n"/>
+      <c r="D19" s="36" t="n"/>
+      <c r="E19" s="36" t="n"/>
+      <c r="F19" s="36" t="n"/>
+      <c r="G19" s="36" t="n"/>
+      <c r="H19" s="37" t="n"/>
     </row>
     <row r="21" ht="60" customHeight="1">
       <c r="A21" s="9" t="inlineStr">
@@ -2501,6 +2633,13 @@
           <t>NOTA METODOLÓGICA. Área y MSAVI 2024 proceden del catálogo maestro de bloques V5/V6. El rango altitudinal y la pendiente promedio proceden del reporte de estadística zonal sobre el MDE («Rango de altitud y Pendiente Promedio por Bloques V6»). El porcentaje de «Vegetación alta» procede de la estadística zonal del NDVI mediana 2025 (Sentinel-2). Los totales y promedios se calculan con fórmulas sobre las filas del cuadro.</t>
         </is>
       </c>
+      <c r="B21" s="36" t="n"/>
+      <c r="C21" s="36" t="n"/>
+      <c r="D21" s="36" t="n"/>
+      <c r="E21" s="36" t="n"/>
+      <c r="F21" s="36" t="n"/>
+      <c r="G21" s="36" t="n"/>
+      <c r="H21" s="37" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="9">
@@ -2524,7 +2663,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E21"/>
+  <dimension ref="A1:E22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -2576,6 +2715,7 @@
         </is>
       </c>
     </row>
+    <row r="7"/>
     <row r="8" ht="18" customHeight="1">
       <c r="A8" s="5" t="inlineStr">
         <is>
@@ -2826,41 +2966,74 @@
         </is>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" s="16" t="inlineStr">
+    <row r="18">
+      <c r="A18" s="34" t="inlineStr">
+        <is>
+          <t>D-09</t>
+        </is>
+      </c>
+      <c r="B18" s="34" t="inlineStr">
+        <is>
+          <t>Distribución areal de clases MSAVI 2024</t>
+        </is>
+      </c>
+      <c r="C18" s="34" t="inlineStr">
+        <is>
+          <t>La hoja «Cobertura MSAVI-NDVI» consignaba «Por determinar» en la distribución areal de clases MSAVI 2024; se incorpora el metrado por clase medido sobre la cartografía temática MSAVI 2024 del bloque: 11.54 % del bloque (12.678 ha) bajo el umbral 0.4976 y 88.46 % sobre el umbral; clase areal dominante «Vigor moderado».</t>
+        </is>
+      </c>
+      <c r="D18" s="33" t="inlineStr">
+        <is>
+          <t>CORREGIDO</t>
+        </is>
+      </c>
+      <c r="E18" s="34" t="inlineStr">
+        <is>
+          <t>Se sustituye «Por determinar» por el metrado por clase. Las hectáreas se derivan del reparto porcentual medido aplicado a la superficie de catálogo (V5/V6) del bloque, por lo que la suma de las cinco clases iguala dicha superficie. Pendiente de refrendo con estadística zonal directa sobre el ráster MSAVI 2024 cuando se disponga del insumo.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19"/>
+    <row r="20">
+      <c r="A20" s="16" t="inlineStr">
         <is>
           <t>RESUMEN</t>
         </is>
       </c>
-      <c r="B19" s="17" t="inlineStr">
-        <is>
-          <t>8 verificaciones</t>
-        </is>
-      </c>
-      <c r="C19" s="17" t="inlineStr">
-        <is>
-          <t>CONFORME: 2 · NO SUSTANTIVA: 2 · SUSTANTIVA: 4</t>
-        </is>
-      </c>
-      <c r="D19" s="17" t="inlineStr"/>
-      <c r="E19" s="17" t="inlineStr"/>
-    </row>
-    <row r="21" ht="60" customHeight="1">
-      <c r="A21" s="9" t="inlineStr">
+      <c r="B20" s="17" t="inlineStr">
+        <is>
+          <t>9 verificaciones</t>
+        </is>
+      </c>
+      <c r="C20" s="17" t="inlineStr">
+        <is>
+          <t>CONFORME: 2 · NO SUSTANTIVA: 2 · SUSTANTIVA: 4 · CORREGIDO: 1</t>
+        </is>
+      </c>
+      <c r="D20" s="17" t="inlineStr"/>
+      <c r="E20" s="17" t="inlineStr"/>
+    </row>
+    <row r="21" ht="60" customHeight="1"/>
+    <row r="22">
+      <c r="A22" s="9" t="inlineStr">
         <is>
           <t>NOTA METODOLÓGICA. Este control se genera de forma reproducible cruzando la ficha DT del bloque (F-DT-01 a F-DT-05) con el catálogo maestro de bloques V5/V6, la estadística zonal de altitud y pendiente sobre el MDE, la estadística zonal del NDVI mediana 2025 y el cruce INEI-Bloques de centros poblados. Una calificación CONFORME acredita que la verificación se ejecutó y no arrojó discrepancia; no equivale a validación de campo del dato.</t>
         </is>
       </c>
+      <c r="B22" s="36" t="n"/>
+      <c r="C22" s="36" t="n"/>
+      <c r="D22" s="36" t="n"/>
+      <c r="E22" s="37" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="8">
-    <mergeCell ref="A21:E21"/>
     <mergeCell ref="A4:E4"/>
     <mergeCell ref="A2:E2"/>
     <mergeCell ref="A1:E1"/>
     <mergeCell ref="A5:E5"/>
     <mergeCell ref="A8:E8"/>
     <mergeCell ref="A6:E6"/>
+    <mergeCell ref="A22:E22"/>
     <mergeCell ref="A3:E3"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
